--- a/bench/data/files/synthetic3_A.xlsx
+++ b/bench/data/files/synthetic3_A.xlsx
@@ -570,17 +570,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Lumen Dynamics</t>
+          <t>Junction Capital</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -590,52 +590,52 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2013-10-10</t>
+          <t>2010-11-19</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2013-09-14</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>105.2</v>
+        <v>1188.4</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>292.4</v>
+        <v>1071.5</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>23.5</v>
+        <v>318.5</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>54</v>
+        <v>381.1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>74.40000000000001</v>
+        <v>561.5</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.517</v>
+        <v>0.291</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Michael O'Brien, Robert Brown, Ravi Williams, Elena Yamamoto, Sophie Rossi</t>
+          <t>Wei Chen, Michael Rossi, Sarah Johnson, Amanda Mueller</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nimbus Logic</t>
+          <t>Atlas Dynamics</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -645,52 +645,52 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2012-05-04</t>
+          <t>2013-01-09</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>2019-07-27</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>67.3</v>
+        <v>1539.6</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>81.40000000000001</v>
+        <v>4701.4</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>16.8</v>
+        <v>216.5</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>39.9</v>
+        <v>428.1</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>69.2</v>
+        <v>410.1</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.958</v>
+        <v>0.223</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Laura Lopez, Ahmed Tanaka</t>
+          <t>Michael Xu, Priya Patel, Jennifer Ueno</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Glacier Pharma</t>
+          <t>Nimbus Materials</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -700,42 +700,42 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2012-09-22</t>
+          <t>2010-12-19</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
+          <t>2016-11-25</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1450.4</v>
+        <v>141.3</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1177.7</v>
+        <v>204.6</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>367.1</v>
+        <v>29.7</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>424.1</v>
+        <v>56.2</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1584.9</v>
+        <v>113</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.529</v>
+        <v>0.851</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Amanda Brown, Sophie Williams</t>
+          <t>Thomas Patel, Daniel Qureshi, Wei Mueller, Christopher Patel, Priya O'Brien</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Glacier Ltd</t>
+          <t>Kepler Materials</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -755,162 +755,154 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2011-10-18</t>
+          <t>2012-02-26</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2019-12-22</t>
+          <t>2015-12-22</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>834.2</v>
+        <v>1419.6</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1694</v>
+        <v>3538.7</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>145.1</v>
+        <v>117.9</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>137.9</v>
+        <v>222.4</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>266.2</v>
+        <v>198.8</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.292</v>
+        <v>0.753</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Yamamoto, Priya Lopez, Olivia Fischer, Christopher Gupta, Wei Lopez</t>
+          <t>Sarah Xu, Olivia Anderson</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Nova Bio</t>
+          <t>Orion Holdings</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2011-06-02</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
+          <t>2010-01-11</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr"/>
       <c r="G10" s="5" t="n">
-        <v>657.1</v>
+        <v>906.7</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1487.7</v>
+        <v/>
       </c>
       <c r="I10" s="5" t="n">
-        <v>168.5</v>
+        <v>183.3</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>284.1</v>
+        <v/>
       </c>
       <c r="K10" s="5" t="n">
-        <v>720.4</v>
+        <v>604.9</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.518</v>
+        <v>0.761</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>David Williams, Amanda Schmidt</t>
+          <t>Priya Ueno, David Davis, Hannah Hassan, Thomas Ivanov</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Quanta Bio</t>
+          <t>Forge Pharma</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2010-02-13</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-18</t>
-        </is>
-      </c>
+          <t>2013-09-12</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="n">
-        <v>1422.4</v>
+        <v>1830.5</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2109.8</v>
+        <v/>
       </c>
       <c r="I11" s="5" t="n">
-        <v>128</v>
+        <v>394.4</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>187.3</v>
+        <v/>
       </c>
       <c r="K11" s="5" t="n">
-        <v>362.3</v>
+        <v>214.1</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.741</v>
+        <v>0.39</v>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Michael Chen, Hannah Patel, Amanda Kim, Olivia Mueller, Laura Xu</t>
+          <t>Olivia Williams, Daniel Gupta, Yuki Yamamoto, Sophie Lopez, Olivia Davis</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Cipher Logic</t>
+          <t>Lumen Materials</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -920,52 +912,52 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>2010-12-18</t>
+          <t>2010-08-03</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2016-09-12</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>792.5</v>
+        <v>1075.3</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1154.3</v>
+        <v>2930.3</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>172.7</v>
+        <v>211.2</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>248</v>
+        <v>239.8</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>690.8</v>
+        <v>197.3</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.645</v>
+        <v>0.223</v>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Thomas Lopez, David Rossi, Matthew Rossi</t>
+          <t>Sarah Rossi, Matthew Fischer, Sarah Rossi, Wei Anderson</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Apex Media</t>
+          <t>Orion Systems</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -975,42 +967,42 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2011-11-03</t>
+          <t>2010-10-05</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>2019-01-11</t>
+          <t>2016-08-10</t>
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>821.4</v>
+        <v>808.7</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>1515.9</v>
+        <v>2262.7</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>217.3</v>
+        <v>156</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>489.4</v>
+        <v>132</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>482.6</v>
+        <v>134.8</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.545</v>
+        <v>0.455</v>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>James Fischer, Ravi Chen, Christopher Nakamura, Andrew Brown</t>
+          <t>Michael Ueno, Sophie Evans, Priya Schmidt, Ahmed Zhang, Emma Nakamura</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Umbra Labs</t>
+          <t>Kepler Partners</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1030,59 +1022,162 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>2013-04-14</t>
+          <t>2012-08-12</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>2020-02-18</t>
+          <t>2015-10-05</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>268.5</v>
+        <v>1583.8</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>725.1</v>
+        <v>4462.7</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>65.8</v>
+        <v>361.8</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>89.3</v>
+        <v>661.1</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>166.4</v>
+        <v>1042</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.918</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Sarah Chen, Jessica Fischer, Thomas Lopez, Amanda Fischer</t>
+          <t>Rachel Vega, Thomas Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Yields Group</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Sydney, AU</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2013-01-09</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>2018-10-23</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Sophie Anderson, Christopher Kim, Jessica Johnson, Amanda Tanaka</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Fund II</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Forge Ltd</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2013-09-04</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2016-11-19</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1058.4</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>2008.4</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>219.2</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>682.4</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Wei Davis, Sophie Yamamoto, Matthew Kim, Ahmed Hassan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Xenith Media</t>
+          <t>Umbra Inc</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1092,107 +1187,103 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2015-05-01</t>
+          <t>2013-03-12</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>2021-05-20</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1401.5</v>
+        <v>487.6</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>4774.5</v>
+        <v>1494.8</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>329</v>
+        <v>51.1</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>463.1</v>
+        <v>46.7</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>331.4</v>
+        <v>57.6</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.838</v>
+        <v>0.909</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Daniel Qureshi, Andrew Qureshi</t>
+          <t>Rachel Schmidt, Wei Kim, Andrew Schmidt, Hannah Chen, Jessica Davis</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Umbra Materials</t>
+          <t>Beacon Group</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
+          <t>2011-05-04</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="n">
-        <v>1246.6</v>
+        <v>926.6</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>1093.5</v>
+        <v/>
       </c>
       <c r="I18" s="5" t="n">
-        <v>112.5</v>
+        <v>90.8</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>180.3</v>
+        <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>420.6</v>
+        <v>233.9</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.979</v>
+        <v>0.512</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Jessica Tanaka, Andrew Tanaka, James Nakamura, Wei Schmidt</t>
+          <t>Wei Ueno, Michael Johnson, Ahmed Lopez</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Media</t>
+          <t>Indigo SA</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1202,52 +1293,52 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2012-04-02</t>
+          <t>2010-11-26</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2020-04-26</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>929.4</v>
+        <v>77.2</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>2086.9</v>
+        <v>84.5</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>103.4</v>
+        <v>15.6</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>226.7</v>
+        <v>25.5</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>390.8</v>
+        <v>34.5</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.655</v>
+        <v>0.429</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Sophie Brown, Rachel Patel, Hannah Anderson, Yuki Evans, Thomas Kim</t>
+          <t>Rachel Davis, Jessica Schmidt, Olivia Schmidt, Michael Patel, Christopher Zhang</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Stratus Labs</t>
+          <t>Stratus Bio</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1257,162 +1348,59 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2015-01-15</t>
+          <t>2012-06-18</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2019-12-26</t>
+          <t>2020-06-30</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1449.3</v>
+        <v>1215.2</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>4471.1</v>
+        <v>4099.9</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>204.5</v>
+        <v>172.2</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>225.5</v>
+        <v>281.7</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>230.9</v>
+        <v>617.2</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.349</v>
+        <v>0.478</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Thomas Fischer, Priya Lopez</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Beacon Media</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Zurich, CH</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>2012-07-07</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>2015-06-25</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>581.5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>1025.1</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>229.4</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>287.2</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>Jennifer Anderson, Yuki Zhang, Sophie Xu, Sarah Davis</t>
+          <t>James Mueller, Jessica Qureshi, Ahmed O'Brien</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Indigo Networks</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>2014-02-17</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-25</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>1806</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>5859.8</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>354.8</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>472.5</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>293.5</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M22" s="5" t="inlineStr">
-        <is>
-          <t>Olivia Fischer, Thomas Kim, Emma Brown, Sarah Davis</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Fund II</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Forge Group</t>
+          <t>Gravity AG</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1422,52 +1410,52 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2014-10-15</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2019-11-17</t>
+          <t>2021-01-05</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>818.8</v>
+        <v>682.7</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>2569.8</v>
+        <v>2084.4</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>131.3</v>
+        <v>147.9</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>248.7</v>
+        <v>221.1</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>454.9</v>
+        <v>330</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Jessica Tanaka, Andrew Chen, Matthew Hassan, Sophie Anderson</t>
+          <t>Michael Vega, Jennifer O'Brien, Matthew Kim, Sophie Schmidt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Vertex Pharma</t>
+          <t>Vertex Energy</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1477,52 +1465,52 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>2014-12-26</t>
+          <t>2014-01-20</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>502.7</v>
+        <v>1847.9</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>870.4</v>
+        <v>1778.4</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>133.3</v>
+        <v>457.7</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>302.9</v>
+        <v>490.8</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>526.7</v>
+        <v>814</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.477</v>
+        <v>0.967</v>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
-          <t>Jessica Ivanov, Jessica Evans</t>
+          <t>Elena O'Brien, Christopher Gupta</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Stratus Pharma</t>
+          <t>Orion Tech</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1532,114 +1520,213 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>2012-01-04</t>
+          <t>2014-06-10</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2019-12-07</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1799.3</v>
+        <v>1294</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1558</v>
+        <v>4378.9</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>335.2</v>
+        <v>333.2</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>765.4</v>
+        <v>463.1</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>425.2</v>
+        <v>1332.5</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.492</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>Olivia Rossi, Christopher Qureshi, Priya Patel, Sophie Johnson, Hannah Ivanov</t>
+          <t>Matthew Anderson, Michael Gupta</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Radial Media</t>
+          <t>Forge Tech</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>2013-07-21</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>2020-09-09</t>
-        </is>
-      </c>
+          <t>2013-09-10</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="n">
-        <v>1074.5</v>
+        <v>951.5</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1574.7</v>
+        <v/>
       </c>
       <c r="I26" s="5" t="n">
-        <v>264.2</v>
+        <v>79.8</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>498.8</v>
+        <v/>
       </c>
       <c r="K26" s="5" t="n">
-        <v>345.4</v>
+        <v>234.4</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.967</v>
+        <v>0.478</v>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
-          <t>Andrew Ueno, Wei Qureshi</t>
+          <t>Priya Patel, Thomas Mueller</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Lumen Bio</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Munich, DE</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2013-11-26</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-04</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1548.7</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>3902</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Ravi Kim, Sophie Ivanov</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Fund III</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Zenith Solutions</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2012-10-21</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2015-07-28</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>1139.8</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1172.1</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>477</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Hannah Ivanov, Rachel Hassan, Ahmed Yamamoto, Priya Davis</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Krypton Ltd</t>
+          <t>Forge Dynamics</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1649,52 +1736,52 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>2016-03-25</t>
+          <t>2012-03-22</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2019-01-05</t>
+          <t>2015-05-07</t>
         </is>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1670.1</v>
+        <v>826.3</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>4661.4</v>
+        <v>1400.2</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>162.3</v>
+        <v>89.2</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>326.8</v>
+        <v>78.3</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>447.7</v>
+        <v>398</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.546</v>
+        <v>0.169</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>Sophie Patel, Sophie Xu, Laura Johnson, Ravi Nakamura, Ahmed Mueller</t>
+          <t>Robert Qureshi, Sarah Xu</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Iris Media</t>
+          <t>Tessera Solutions</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1704,93 +1791,97 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>2016-03-03</t>
+          <t>2014-09-26</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2023-04-15</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1609.3</v>
+        <v>939.4</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>4413</v>
+        <v>2457.2</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>191.6</v>
+        <v>126.3</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>424.5</v>
+        <v>229.8</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>225.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.851</v>
+        <v>0.904</v>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
-          <t>Priya Rossi, Sarah Gupta, Elena Fischer</t>
+          <t>Thomas Yamamoto, Mark Patel, Rachel Anderson</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Echo Solutions</t>
+          <t>Polaris Logistics</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2015-04-28</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr"/>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>2018-06-18</t>
+        </is>
+      </c>
       <c r="G31" s="5" t="n">
-        <v>718.3</v>
+        <v>1341.2</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v/>
+        <v>1156.8</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>155.2</v>
+        <v>218.1</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v/>
+        <v>300.1</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>107.9</v>
+        <v>541.3</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.637</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Mark Ueno, Priya Chen, David Brown, Amanda Schmidt</t>
+          <t>Yuki Davis, Sarah Kim, Amanda Yamamoto, Ahmed Brown, Jennifer Hassan</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Kepler Energy</t>
+          <t>Forge Health</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -1800,62 +1891,58 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2017-04-24</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>2021-02-23</t>
-        </is>
-      </c>
+          <t>2013-10-16</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
       <c r="G32" s="5" t="n">
-        <v>1867.2</v>
+        <v>748.2</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>1391.5</v>
+        <v/>
       </c>
       <c r="I32" s="5" t="n">
-        <v>330.3</v>
+        <v>189.8</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>489.5</v>
+        <v/>
       </c>
       <c r="K32" s="5" t="n">
-        <v>681.4</v>
+        <v>199.2</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.731</v>
+        <v>0.754</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Matthew Schmidt, Andrew Qureshi, Elena Qureshi</t>
+          <t>Sophie Davis, Priya Rossi</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Polaris Holdings</t>
+          <t>Xenith Energy</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1865,47 +1952,47 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2015-08-19</t>
+          <t>2013-09-15</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2017-06-30</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1580.8</v>
+        <v>319.1</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>3977.8</v>
+        <v>397</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>343.8</v>
+        <v>27.2</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>811.5</v>
+        <v>54.3</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>543.5</v>
+        <v>112.8</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.57</v>
+        <v>0.254</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>Yuki Ivanov, Andrew Hassan</t>
+          <t>Daniel Zhang, Wei Johnson, Ravi Ueno, Wei Qureshi, Matthew Ueno</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Radial Corp</t>
+          <t>Forge AG</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -1915,53 +2002,57 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr"/>
+          <t>2014-08-04</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>2021-07-11</t>
+        </is>
+      </c>
       <c r="G34" s="5" t="n">
-        <v>693.6</v>
+        <v>964.5</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v/>
+        <v>2397.7</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>89.8</v>
+        <v>138.6</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v/>
+        <v>274.3</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>101.5</v>
+        <v>289.2</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.51</v>
+        <v>0.694</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Emma Tanaka, Emma Gupta, Sarah Rossi</t>
+          <t>Michael Fischer, Emma Schmidt</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Delta Tech</t>
+          <t>Delta Health</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1971,52 +2062,52 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2014-05-04</t>
+          <t>2014-05-22</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2021-04-10</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1128.5</v>
+        <v>492</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1717.6</v>
+        <v>696.1</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>270.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>674.9</v>
+        <v>124.9</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>551.8</v>
+        <v>77.3</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.351</v>
+        <v>0.15</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Thomas Schmidt, Mark Brown, Ravi Lopez, Yuki Nakamura</t>
+          <t>David Qureshi, Andrew Brown, Robert Nakamura</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Beacon SA</t>
+          <t>Yields Systems</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2026,52 +2117,52 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-27</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>820</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>1706.3</v>
+        <v>171.7</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>121.8</v>
+        <v>20.2</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>159.2</v>
+        <v>40.4</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>174.7</v>
+        <v>53.1</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.92</v>
+        <v>0.582</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Sophie Vega, Sophie O'Brien, Laura Hassan, Mark Rossi</t>
+          <t>Sarah Davis, Ahmed Tanaka, Ravi Brown, Ahmed Evans, Olivia Schmidt</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Atlas Networks</t>
+          <t>Cobalt Logistics</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2081,52 +2172,52 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2015-06-12</t>
+          <t>2014-11-26</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2018-06-02</t>
+          <t>2020-02-14</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>647.6</v>
+        <v>983.7</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>1318.3</v>
+        <v>2951.9</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>145.3</v>
+        <v>227</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>250.9</v>
+        <v>398.1</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>411.3</v>
+        <v>958.1</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.896</v>
+        <v>0.744</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Amanda Vega, James Zhang, Wei Qureshi</t>
+          <t>Robert Hassan, Michael Kim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Ember Logistics</t>
+          <t>Ember GmbH</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2136,52 +2227,52 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2017-04-20</t>
+          <t>2015-07-25</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-07-17</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>339.9</v>
+        <v>1375</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>576.8</v>
+        <v>2453.4</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>65.09999999999999</v>
+        <v>250.5</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>135.9</v>
+        <v>389.2</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>52.3</v>
+        <v>584.3</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.929</v>
+        <v>0.246</v>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Jessica Mueller, Sarah Davis, Andrew Chen, Olivia Kim, James Williams</t>
+          <t>Rachel Lopez, Priya Gupta, Mark Schmidt, Amanda Davis</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Lumen Health</t>
+          <t>Ember Ltd</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2191,52 +2282,52 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2014-03-24</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2019-03-23</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1740.7</v>
+        <v>1646.8</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>6084.3</v>
+        <v>5130.7</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>457.5</v>
+        <v>338.9</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>747</v>
+        <v>478.5</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>2039.4</v>
+        <v>1335.4</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.734</v>
+        <v>0.368</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Michael Ueno, Yuki Vega, Ahmed Evans, Laura Anderson, Ravi Lopez</t>
+          <t>James Mueller, Laura Xu, Emma Hassan, Robert Johnson, Sophie Nakamura</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Lumen Logistics</t>
+          <t>Forge Materials</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2246,52 +2337,52 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>2016-02-23</t>
+          <t>2014-02-15</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2021-02-11</t>
+          <t>2022-03-18</t>
         </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>884.7</v>
+        <v>1123.7</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>2226.8</v>
+        <v>2930.9</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>242.9</v>
+        <v>268.6</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>243.3</v>
+        <v>235.9</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>819.7</v>
+        <v>758.3</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.456</v>
+        <v>0.159</v>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Xu, James Ivanov</t>
+          <t>Olivia Gupta, Emma Rossi, Priya Hassan, Elena Nakamura, Matthew Vega</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Kepler Inc</t>
+          <t>Radial Foods</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -2301,162 +2392,59 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="G41" s="5" t="n">
-        <v>366.7</v>
+        <v>829.7</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>924.9</v>
+        <v>2507.5</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>38.4</v>
+        <v>196.4</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>33.9</v>
+        <v>448.4</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>111.1</v>
+        <v>200.1</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.553</v>
+        <v>0.946</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>Matthew Yamamoto, Emma Zhang, Robert Kim</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>Tessera Systems</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>2016-05-06</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>2019-03-05</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>378</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>452.7</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>117.1</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Robert Qureshi, Andrew Davis, Yuki Schmidt, Daniel Schmidt</t>
+          <t>Michael Evans, Ahmed Lopez, Priya Qureshi</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Zenith Capital</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>2015-09-03</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>1630.9</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>4671.1</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>358.9</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>509.6</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>1110.8</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Fischer, Amanda Anderson, Amanda Anderson, James Mueller</t>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Fund III</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Junction Industries</t>
+          <t>Glacier Materials</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2466,52 +2454,52 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2016-06-12</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2021-07-26</t>
+          <t>2018-04-29</t>
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>328.9</v>
+        <v>1114.8</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>795.3</v>
+        <v>3395.3</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>79.3</v>
+        <v>224.3</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>115.7</v>
+        <v>321.9</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>111.2</v>
+        <v>512.4</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.328</v>
+        <v>0.753</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>David Nakamura, Mark Xu</t>
+          <t>Robert Gupta, Mark Schmidt, Olivia Ueno, Olivia Nakamura, David Tanaka</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Ember Networks</t>
+          <t>Junction Materials</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -2521,42 +2509,42 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2016-04-13</t>
+          <t>2015-04-07</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="G45" s="5" t="n">
-        <v>398.1</v>
+        <v>1378.2</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>760.5</v>
+        <v>2802.4</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>67.5</v>
+        <v>250.9</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>282.9</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>223.9</v>
+        <v>344.5</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.364</v>
+        <v>0.607</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Michael Mueller, James Zhang, James Williams</t>
+          <t>Mark Hassan, Ahmed Yamamoto, Sarah Fischer</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Glacier Holdings</t>
+          <t>Apex Industries</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -2566,7 +2554,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2576,107 +2564,103 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2016-02-17</t>
+          <t>2014-12-04</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2019-02-10</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1743</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>2029.5</v>
+        <v>173.1</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>226.4</v>
+        <v>17.3</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>547.4</v>
+        <v>32.7</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>848.8</v>
+        <v>50.1</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.423</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Thomas O'Brien, Rachel Ivanov, Jennifer Patel</t>
+          <t>Olivia Johnson, Jessica Schmidt, James Williams</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Drift Materials</t>
+          <t>Umbra Corp</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>2021-08-05</t>
-        </is>
-      </c>
+          <t>2017-09-20</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr"/>
       <c r="G47" s="5" t="n">
-        <v>497.2</v>
+        <v>918.1</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1268.2</v>
+        <v/>
       </c>
       <c r="I47" s="5" t="n">
-        <v>41.2</v>
+        <v>128.6</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>57</v>
+        <v/>
       </c>
       <c r="K47" s="5" t="n">
-        <v>123.1</v>
+        <v>153.7</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.399</v>
+        <v>0.749</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Thomas Xu, Ahmed Rossi</t>
+          <t>Ahmed Mueller, Sarah Evans, Laura Hassan, Priya Yamamoto, Priya Anderson</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Orion Health</t>
+          <t>Zenith Inc</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2686,114 +2670,217 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2017-02-05</t>
+          <t>2016-02-18</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2019-12-04</t>
+          <t>2019-02-11</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>791.2</v>
+        <v>1204.6</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>2065.9</v>
+        <v>2569.8</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>187.9</v>
+        <v>117.5</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>452</v>
+        <v>181</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>270.6</v>
+        <v>524.7</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.21</v>
+        <v>0.889</v>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Mark Zhang, Sophie Patel, Ahmed Patel, Sarah Schmidt</t>
+          <t>Thomas Qureshi, Emma Mueller, Laura Mueller, Michael Xu, Robert Fischer</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Halo Corp</t>
+          <t>Quanta Group</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>2017-08-18</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>353.2</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>650.3</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>223.8</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Sophie Fischer, James Schmidt, Ravi Williams, Daniel O'Brien, Daniel Hassan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Xenith Materials</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Sydney, AU</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>2014-10-17</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>2022-12-23</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>580</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>1035</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>456.4</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
+          <t>James Schmidt, Wei O'Brien</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Junction Media</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>2016-12-24</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>860.9</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>1824.8</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>138.4</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>255.9</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Matthew Gupta, Jessica Rossi, Elena Davis</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Fund IV</t>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo, JP</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>2014-06-20</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2018-07-26</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>617.6</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>537.4</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>153.3</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>245.9</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>276.8</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Rossi, Christopher Vega, Mark Chen, Andrew Qureshi, Rachel O'Brien</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Umbra Holdings</t>
+          <t>Halo Logistics</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -2803,52 +2890,52 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2014-09-18</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>651.8</v>
+        <v>1181.2</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>1906.5</v>
+        <v>2223.8</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>133.5</v>
+        <v>195.1</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>307</v>
+        <v>194.9</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>277.1</v>
+        <v>524.2</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.378</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>Matthew Nakamura, James Schmidt, Matthew Patel</t>
+          <t>Ahmed Anderson, Ravi Evans, Michael Anderson, Ahmed Anderson, Emma Rossi</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Group</t>
+          <t>Wavelength Inc</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -2858,52 +2945,52 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>2017-02-28</t>
+          <t>2017-06-12</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1649.8</v>
+        <v>1953.4</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>1516.9</v>
+        <v>2062.9</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>149.7</v>
+        <v>296.4</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>122.5</v>
+        <v>406.1</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>291.7</v>
+        <v>1096.6</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.749</v>
+        <v>0.496</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Tanaka, Matthew Chen</t>
+          <t>Daniel Schmidt, Jessica Mueller</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Ember Holdings</t>
+          <t>Wavelength Group</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2913,52 +3000,52 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2017-08-08</t>
+          <t>2014-06-02</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2021-06-27</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1581.8</v>
+        <v>676.2</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>3229.8</v>
+        <v>1635.9</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>417.9</v>
+        <v>73.8</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>951.7</v>
+        <v>154.6</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1851.6</v>
+        <v>330</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.182</v>
+        <v>0.283</v>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Yuki Kim, Olivia Anderson, Ravi Hassan, Amanda Lopez</t>
+          <t>Jessica Evans, James Ivanov, Daniel Anderson</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Echo Media</t>
+          <t>Junction Networks</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -2968,42 +3055,42 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2019-06-11</t>
+          <t>2014-09-07</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1313</v>
+        <v>88.2</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>1774.7</v>
+        <v>204.9</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>231</v>
+        <v>8.9</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>487.5</v>
+        <v>18.8</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>704.8</v>
+        <v>11.9</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.212</v>
+        <v>0.642</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Jessica Mueller, Elena Evans, Michael Williams</t>
+          <t>Jennifer Evans, Andrew Williams, Thomas Patel, Sarah Johnson, Christopher Anderson</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Lattice Materials</t>
+          <t>Gravity Networks</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
@@ -3013,7 +3100,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3023,52 +3110,52 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2019-05-28</t>
+          <t>2014-01-05</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2018-03-19</t>
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>992.1</v>
+        <v>297.3</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>1004.8</v>
+        <v>565.2</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>256.6</v>
+        <v>57.4</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>233.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>456.8</v>
+        <v>211.4</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.37</v>
+        <v>0.275</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Amanda Qureshi, Jessica Xu, Amanda Xu</t>
+          <t>Matthew Davis, Ahmed Anderson</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Polaris Health</t>
+          <t>Atlas Solutions</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3078,52 +3165,52 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>2014-10-22</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2021-04-22</t>
+          <t>2021-07-30</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1709.2</v>
+        <v>188.6</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>1624.1</v>
+        <v>654.9</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>262.5</v>
+        <v>21.2</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>619.7</v>
+        <v>37.5</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>827.2</v>
+        <v>55.4</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.531</v>
+        <v>0.188</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Michael Chen, Matthew Xu</t>
+          <t>Emma Qureshi, Sarah Chen</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Group</t>
+          <t>Halo Ltd</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3133,42 +3220,42 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2016-07-07</t>
+          <t>2014-01-19</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2019-09-13</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>249.7</v>
+        <v>1006.3</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>458.6</v>
+        <v>2147.6</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>37.5</v>
+        <v>143.7</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>85.8</v>
+        <v>341.6</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>56.8</v>
+        <v>120.9</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.709</v>
+        <v>0.961</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Wei Yamamoto, Andrew Lopez</t>
+          <t>Daniel Ivanov, Jennifer Kim, Laura Anderson</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Bloom Dynamics</t>
+          <t>Nova Pharma</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -3178,7 +3265,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3188,52 +3275,52 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2016-10-21</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2020-11-14</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>871.4</v>
+        <v>1152.3</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>2502.9</v>
+        <v>2771.2</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>116.7</v>
+        <v>223.6</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>257.9</v>
+        <v>355.4</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>455.4</v>
+        <v>265.7</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.663</v>
+        <v>0.479</v>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Ravi Evans, Elena Anderson, Michael Hassan, Matthew Vega, Christopher Williams</t>
+          <t>Robert Davis, Thomas Ueno</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Helix AG</t>
+          <t>Polaris SA</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -3243,52 +3330,52 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2019-11-01</t>
+          <t>2017-01-28</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1991</v>
+        <v>1731.1</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>6137.8</v>
+        <v>6037.9</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>461.6</v>
+        <v>221</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>469.3</v>
+        <v>333.8</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>255.2</v>
+        <v>721</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.432</v>
+        <v>0.742</v>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Robert Ueno, Daniel Anderson, Rachel Hassan, Sarah Davis</t>
+          <t>Sarah Hassan, Rachel Brown, Jennifer Chen, Andrew Xu</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Drift Energy</t>
+          <t>Halo Health</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3298,52 +3385,52 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
+          <t>2014-12-03</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1449.2</v>
+        <v>925.4</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>3455.4</v>
+        <v>1886.4</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>205.3</v>
+        <v>135.9</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>220.5</v>
+        <v>128.5</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>460.4</v>
+        <v>575.3</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.322</v>
+        <v>0.653</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Matthew Fischer, Ahmed Hassan, Thomas Ivanov</t>
+          <t>James O'Brien, Sarah Vega, Olivia Anderson</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Umbra Dynamics</t>
+          <t>Junction Foods</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3353,52 +3440,52 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2016-11-02</t>
+          <t>2014-10-18</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2021-12-12</t>
+          <t>2020-07-25</t>
         </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>987.4</v>
+        <v>405.2</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>1517.5</v>
+        <v>1197.5</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>171.1</v>
+        <v>83.5</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>164.9</v>
+        <v>114.3</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>768.4</v>
+        <v>302</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.271</v>
+        <v>0.344</v>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Yuki Johnson, Wei Patel, Olivia Mueller</t>
+          <t>Jennifer Johnson, Jessica Xu, Elena Rossi, Michael Xu</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Vertex Corp</t>
+          <t>Beacon Tech</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3408,52 +3495,52 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2019-11-22</t>
+          <t>2014-12-13</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2024-01-20</t>
+          <t>2020-09-20</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>613.8</v>
+        <v>1169.1</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>2065.7</v>
+        <v>1051.8</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>160.4</v>
+        <v>195.1</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>238.1</v>
+        <v>203</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>101</v>
+        <v>683.6</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.254</v>
+        <v>0.277</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Yuki Vega, Wei Yamamoto, Olivia Davis, Priya Tanaka, Amanda Nakamura</t>
+          <t>Emma Fischer, David Nakamura</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Cipher Labs</t>
+          <t>Ember Solutions</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3463,52 +3550,52 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>2017-08-09</t>
+          <t>2015-10-18</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2018-09-19</t>
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>527.6</v>
+        <v>1189.3</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>1639.5</v>
+        <v>1413.6</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>138</v>
+        <v>213.7</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>166.5</v>
+        <v>243.4</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>417.8</v>
+        <v>604.8</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.337</v>
+        <v>0.477</v>
       </c>
       <c r="M64" s="5" t="inlineStr">
         <is>
-          <t>Daniel Tanaka, Hannah Fischer, Jennifer Rossi, Ahmed Mueller, Elena Gupta</t>
+          <t>Priya Williams, Olivia Rossi, Emma Vega, Hannah Ivanov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Polaris Capital</t>
+          <t>Echo Industries</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3518,107 +3605,103 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>2016-08-20</t>
+          <t>2016-01-16</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>1147.3</v>
+        <v>1584.3</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>3116</v>
+        <v>4517.1</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>117</v>
+        <v>127.2</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>133.4</v>
+        <v>138.1</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>110.7</v>
+        <v>178.9</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.739</v>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Anderson, Emma Tanaka, Michael Mueller, Sarah Zhang</t>
+          <t>David Xu, Sarah Ueno</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Meridian Solutions</t>
+          <t>Ember Networks</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
+          <t>2014-05-11</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr"/>
       <c r="G66" s="5" t="n">
-        <v>1605.3</v>
+        <v>1164.4</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>4100.7</v>
+        <v/>
       </c>
       <c r="I66" s="5" t="n">
-        <v>200</v>
+        <v>318.1</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>297.1</v>
+        <v/>
       </c>
       <c r="K66" s="5" t="n">
-        <v>455.4</v>
+        <v>1165.8</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.368</v>
+        <v>0.971</v>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
-          <t>Laura Schmidt, Sarah Brown, Hannah Lopez</t>
+          <t>James Zhang, Olivia Johnson, Andrew Evans, Hannah Brown, Michael Zhang</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Beacon Networks</t>
+          <t>Halo Dynamics</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3628,52 +3711,52 @@
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>2018-03-27</t>
+          <t>2017-04-14</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>376.4</v>
+        <v>1036.4</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>802.2</v>
+        <v>3001</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>42.7</v>
+        <v>155.7</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>64</v>
+        <v>170.9</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>111.6</v>
+        <v>491</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.802</v>
+        <v>0.944</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t>Elena Yamamoto, Ravi Schmidt, Ahmed Tanaka</t>
+          <t>Matthew Schmidt, James Ivanov</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Junction Ltd</t>
+          <t>Stratus Labs</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3683,213 +3766,114 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>2018-04-01</t>
+          <t>2017-03-17</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>2022-06-10</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>315.2</v>
+        <v>1840.8</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>1023.4</v>
+        <v>3469.7</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>41.7</v>
+        <v>382.4</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>33.9</v>
+        <v>309.3</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>109.1</v>
+        <v>373.9</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.293</v>
+        <v>0.167</v>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>Priya Rossi, Sophie Lopez, Robert Schmidt, Mark Hassan</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Kepler Partners</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Atlanta, GA</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-11</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>1681.8</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>4555.2</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>257.9</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>587.8</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>186.1</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0.946</v>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>Sophie Qureshi, Mark Vega, Olivia Davis, Andrew Yamamoto</t>
+          <t>Hannah Anderson, Amanda O'Brien</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Meridian Media</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>2016-07-09</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>2019-07-22</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="H70" s="5" t="n">
-        <v>2570.7</v>
-      </c>
-      <c r="I70" s="5" t="n">
-        <v>135.6</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>169.4</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
-        <is>
-          <t>Jennifer Gupta, James Vega, Jennifer Qureshi, Mark Ueno</t>
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Fund IV</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Apex Logistics</t>
+          <t>Stratus Logistics</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr"/>
+          <t>2019-07-19</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>2024-09-24</t>
+        </is>
+      </c>
       <c r="G71" s="5" t="n">
-        <v>361.7</v>
+        <v>1754.1</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v/>
+        <v>5744.1</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>381.3</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v/>
+        <v>326.5</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>327.6</v>
+        <v>1640.9</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.195</v>
+        <v>0.677</v>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
-          <t>Daniel Xu, Rachel O'Brien, David Yamamoto, Wei Fischer, Michael Schmidt</t>
+          <t>Emma Qureshi, Sophie Schmidt, Olivia Kim, Wei Qureshi</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Fathom Solutions</t>
+          <t>Junction Bio</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3899,47 +3883,47 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
+          <t>2018-02-09</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2025-01-25</t>
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1660.7</v>
+        <v>151.1</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>4244.9</v>
+        <v>337.6</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>272.5</v>
+        <v>39.1</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>361.8</v>
+        <v>59</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>323</v>
+        <v>172.5</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.925</v>
+        <v>0.436</v>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
-          <t>Thomas Brown, Emma Chen, Andrew Nakamura</t>
+          <t>David Yamamoto, Elena Chen, Andrew Tanaka, Michael Chen</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Stratus Partners</t>
+          <t>Drift Foods</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -3954,52 +3938,52 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>2019-07-28</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>305.4</v>
+        <v>1813.9</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>361.9</v>
+        <v>5216.3</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>49.3</v>
+        <v>488.3</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>548.9</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>212.6</v>
+        <v>1473.2</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.29</v>
+        <v>0.63</v>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
-          <t>Elena Brown, Rachel Brown, Thomas Vega, Michael Davis</t>
+          <t>Jennifer Lopez, Andrew Anderson</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Meridian Tech</t>
+          <t>Zenith SA</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4009,52 +3993,52 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>2019-03-14</t>
+          <t>2017-09-10</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>1327.8</v>
+        <v>723.9</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>1170.6</v>
+        <v>2486.6</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>325.4</v>
+        <v>176.2</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>290.6</v>
+        <v>361.8</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>710.6</v>
+        <v>241.9</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.897</v>
+        <v>0.998</v>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
-          <t>Laura Brown, Ravi Davis, Yuki Schmidt, Jennifer Tanaka, Thomas Schmidt</t>
+          <t>Ahmed Kim, Andrew Fischer, Matthew Johnson, Jessica Qureshi, Mark Gupta</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Indigo Health</t>
+          <t>Drift Partners</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4064,52 +4048,52 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>2017-04-21</t>
+          <t>2018-06-07</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>2022-02-07</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>1427.3</v>
+        <v>1846.6</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>2678.5</v>
+        <v>6222.4</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>177.7</v>
+        <v>206.4</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>258.2</v>
+        <v>432.2</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>710.1</v>
+        <v>384.2</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.256</v>
+        <v>0.595</v>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
-          <t>Rachel Fischer, Yuki Hassan, Matthew Johnson</t>
+          <t>Hannah Mueller, Matthew Zhang</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Meridian Ltd</t>
+          <t>Umbra Capital</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4119,107 +4103,103 @@
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>2017-08-06</t>
+          <t>2019-03-18</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>135</v>
+        <v>1893.6</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>421.8</v>
+        <v>5852.2</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>31.9</v>
+        <v>469.8</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>63.9</v>
+        <v>553.2</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>90.2</v>
+        <v>1132.2</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.929</v>
+        <v>0.991</v>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
-          <t>Jessica Williams, Rachel Yamamoto</t>
+          <t>David Ivanov, Elena Davis</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Vertex Tech</t>
+          <t>Lattice Capital</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>2018-08-10</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
+          <t>2016-01-08</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr"/>
       <c r="G77" s="5" t="n">
-        <v>655.2</v>
+        <v>1450.8</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>1702.5</v>
+        <v/>
       </c>
       <c r="I77" s="5" t="n">
-        <v>164.8</v>
+        <v>321</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>204.7</v>
+        <v/>
       </c>
       <c r="K77" s="5" t="n">
-        <v>583.6</v>
+        <v>337.7</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.969</v>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Lopez, Laura Lopez, Priya Hassan, Andrew Brown</t>
+          <t>Christopher Patel, Robert Gupta</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Vertex Logistics</t>
+          <t>Xenith Partners</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -4229,52 +4209,52 @@
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>2017-01-26</t>
+          <t>2016-07-09</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>202.4</v>
+        <v>632.5</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>307.2</v>
+        <v>627.7</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>30.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>67</v>
+        <v>164.8</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>53.5</v>
+        <v>346.3</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.355</v>
+        <v>0.726</v>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
-          <t>Michael Brown, Sophie Rossi, Ahmed Chen</t>
+          <t>Jessica Johnson, David Schmidt</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Yields Foods</t>
+          <t>Delta Capital</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -4284,42 +4264,42 @@
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>2016-02-05</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>2021-02-02</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>841.1</v>
+        <v>1228.6</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>2764</v>
+        <v>1673</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>109.9</v>
+        <v>245.5</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>170.1</v>
+        <v>543.8</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>494.5</v>
+        <v>666.6</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.997</v>
+        <v>0.53</v>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
-          <t>Matthew Nakamura, Robert Xu</t>
+          <t>David Evans, Daniel Xu, Ahmed Gupta, Emma Brown, Matthew Chen</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Delta Materials</t>
+          <t>Polaris AG</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
@@ -4329,7 +4309,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -4339,52 +4319,52 @@
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>2018-08-17</t>
+          <t>2019-08-03</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>101.2</v>
+        <v>1100.7</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>173.8</v>
+        <v>3454</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>19.8</v>
+        <v>146.2</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>43.7</v>
+        <v>356.1</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>82.90000000000001</v>
+        <v>250.2</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.984</v>
+        <v>0.408</v>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
-          <t>Yuki Hassan, Jennifer Yamamoto, Laura Evans</t>
+          <t>Mark Anderson, Yuki Xu, Emma Ivanov, Emma Gupta, Amanda Patel</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Delta Health</t>
+          <t>Meridian Dynamics</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -4394,52 +4374,52 @@
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1999.5</v>
+        <v>506.2</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>6183.6</v>
+        <v>437.2</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>313.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>457.7</v>
+        <v>107.1</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>869.5</v>
+        <v>137.5</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.771</v>
+        <v>0.299</v>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
-          <t>Rachel Fischer, Sophie Nakamura, Thomas O'Brien, Thomas Gupta, Hannah Mueller</t>
+          <t>Emma Zhang, Mark Johnson, Wei Williams, Thomas Nakamura, Sarah Vega</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Xenith Health</t>
+          <t>Kepler Foods</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -4449,52 +4429,52 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>2016-04-14</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>2021-01-31</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="G82" s="5" t="n">
-        <v>1199.4</v>
+        <v>147.1</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>1639</v>
+        <v>445</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>286.9</v>
+        <v>13.8</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>538.9</v>
+        <v>13.5</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>1031.2</v>
+        <v>11.3</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.975</v>
+        <v>0.674</v>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
-          <t>Yuki Xu, Rachel Rossi, Olivia Schmidt, James Davis</t>
+          <t>Priya Zhang, Jennifer Williams</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Nova Industries</t>
+          <t>Apex Bio</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -4504,165 +4484,264 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>2016-09-13</t>
+          <t>2017-08-16</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="G83" s="5" t="n">
-        <v>952.4</v>
+        <v>129.6</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>3241.8</v>
+        <v>279.3</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>101</v>
+        <v>28.1</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>129.5</v>
+        <v>65</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>117.6</v>
+        <v>84.8</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>0.249</v>
+        <v>0.397</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
-          <t>Yuki Yamamoto, Laura Patel, Thomas Tanaka, Olivia Johnson, Yuki Kim</t>
+          <t>Mark Schmidt, Wei Xu, Mark Evans, Andrew Davis</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Iris Industries</t>
+          <t>Polaris Group</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>2017-03-01</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>2022-04-26</t>
-        </is>
-      </c>
+          <t>2017-01-16</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr"/>
       <c r="G84" s="5" t="n">
-        <v>588.4</v>
+        <v>1462.8</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>1203.6</v>
+        <v/>
       </c>
       <c r="I84" s="5" t="n">
-        <v>68.2</v>
+        <v>295.7</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>158.9</v>
+        <v/>
       </c>
       <c r="K84" s="5" t="n">
-        <v>48.4</v>
+        <v>1163.2</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.747</v>
+        <v>0.161</v>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
-          <t>Jessica Xu, Rachel Johnson</t>
+          <t>Daniel Anderson, Yuki Mueller, Amanda Schmidt</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Junction Pharma</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>2016-12-23</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-04</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>1109.2</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>2722</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>187</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>255.7</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>440.4</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
+          <t>Priya Kim, Wei Ueno</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
-        <is>
-          <t>Fund V</t>
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Apex Logistics</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>2016-02-03</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr"/>
+      <c r="G86" s="5" t="n">
+        <v>544.2</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
+          <t>Rachel Nakamura, Emma Anderson, Michael Nakamura</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>Echo Health</t>
+          <t>Beacon Inc</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>2019-06-19</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr"/>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
       <c r="G87" s="5" t="n">
-        <v>963.8</v>
+        <v>1709.1</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v/>
+        <v>2199.3</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>164.8</v>
+        <v>311.1</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v/>
+        <v>318.2</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>571.9</v>
+        <v>939.3</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0.527</v>
+        <v>0.352</v>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
-          <t>Elena Evans, Christopher Schmidt, Ahmed Rossi, Sarah Nakamura, Emma Mueller</t>
+          <t>Yuki Schmidt, Daniel Hassan, Andrew Anderson, Ravi Brown</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Zenith Pharma</t>
+          <t>Apex SA</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4672,162 +4751,59 @@
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
+          <t>2017-06-07</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>680.7</v>
+        <v>363.2</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>703.6</v>
+        <v>292.5</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>149.9</v>
+        <v>62.9</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>282.9</v>
+        <v>59.9</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>510.8</v>
+        <v>60.8</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>0.509</v>
+        <v>0.86</v>
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
-          <t>Priya Zhang, Mark Zhang, Wei Lopez, Hannah Kim</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
-        <is>
-          <t>Zenith Inc</t>
-        </is>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>900</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>2485.4</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>201.4</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>263.2</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>147.5</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="M89" s="5" t="inlineStr">
-        <is>
-          <t>Michael O'Brien, Ravi Kim, Sophie Patel, Mark Fischer</t>
+          <t>James Kim, Hannah Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>Indigo SA</t>
-        </is>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>2018-12-02</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>1055.4</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>2007.1</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>252.8</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>568.5</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>293.3</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>0.849</v>
-      </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>Wei Hassan, Ravi Rossi</t>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Fund V</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Apex Corp</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4837,98 +4813,102 @@
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>2020-02-20</t>
+          <t>2021-10-03</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="G91" s="5" t="n">
-        <v>417.7</v>
+        <v>1750.6</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>1427.6</v>
+        <v>4452</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>35.1</v>
+        <v>372.8</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>85</v>
+        <v>472.4</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>32.9</v>
+        <v>1175.6</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
-          <t>Sophie Gupta, Jennifer Yamamoto, Laura Vega, Emma Ueno, Olivia Brown</t>
+          <t>Amanda Mueller, Hannah Fischer</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Tessera Holdings</t>
+          <t>Fathom Materials</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>2019-02-03</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="inlineStr"/>
+          <t>2021-05-21</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
       <c r="G92" s="5" t="n">
-        <v>110</v>
+        <v>1821.6</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v/>
+        <v>3306.2</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>17.8</v>
+        <v>504.9</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v/>
+        <v>1161.9</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>62.5</v>
+        <v>1136.4</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0.584</v>
+        <v>0.237</v>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
-          <t>Matthew O'Brien, Matthew O'Brien, Olivia Nakamura</t>
+          <t>Michael Rossi, Elena Ivanov, Olivia Hassan</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Glacier SA</t>
+          <t>Cobalt SA</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -4943,150 +4923,158 @@
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>2021-12-18</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr"/>
       <c r="G93" s="5" t="n">
-        <v>1029.9</v>
+        <v>1324.7</v>
       </c>
       <c r="H93" s="5" t="n">
         <v/>
       </c>
       <c r="I93" s="5" t="n">
-        <v>200.4</v>
+        <v>311.9</v>
       </c>
       <c r="J93" s="5" t="n">
         <v/>
       </c>
       <c r="K93" s="5" t="n">
-        <v>705.9</v>
+        <v>835.2</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.876</v>
+        <v>0.331</v>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
-          <t>Andrew Williams, Priya Schmidt, Daniel Fischer, Daniel Yamamoto</t>
+          <t>Daniel Nakamura, Laura Kim, Jennifer Schmidt, Sarah Chen, Robert Evans</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Indigo Media</t>
+          <t>Quanta Health</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>2020-11-07</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr"/>
+          <t>2019-12-25</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>2023-12-29</t>
+        </is>
+      </c>
       <c r="G94" s="5" t="n">
-        <v>134.3</v>
+        <v>96.2</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v/>
+        <v>106.4</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>11.6</v>
+        <v>23.4</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v/>
+        <v>30.8</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>45.6</v>
+        <v>21.4</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0.639</v>
+        <v>0.441</v>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
-          <t>Sophie Johnson, Andrew Qureshi</t>
+          <t>Wei Ivanov, Matthew Xu</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Meridian Group</t>
+          <t>Cobalt Ltd</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>2018-07-20</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr"/>
+          <t>2020-02-22</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-17</t>
+        </is>
+      </c>
       <c r="G95" s="5" t="n">
-        <v>764.7</v>
+        <v>1636</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v/>
+        <v>3836</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>126.9</v>
+        <v>422.9</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v/>
+        <v>891.6</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>133.8</v>
+        <v>1132.1</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0.328</v>
+        <v>0.209</v>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
-          <t>Amanda Tanaka, Sophie Gupta, Jessica Kim, Olivia Yamamoto, Olivia Chen</t>
+          <t>Andrew Lopez, David Qureshi, Andrew Lopez, Rachel Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Beacon Systems</t>
+          <t>Ember Labs</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -5096,107 +5084,103 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>2018-11-06</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="G96" s="5" t="n">
-        <v>219</v>
+        <v>1335.1</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>292.6</v>
+        <v>4275.9</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>37.5</v>
+        <v>308.8</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>57.9</v>
+        <v>258.6</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>133</v>
+        <v>1088.6</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>0.719</v>
+        <v>0.511</v>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
-          <t>Rachel Tanaka, James Yamamoto, Ravi Davis, Ahmed Fischer, Yuki Rossi</t>
+          <t>Hannah Zhang, David Yamamoto, Christopher Mueller, Rachel Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Forge Industries</t>
+          <t>Vertex Bio</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>2020-11-09</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
+          <t>2021-03-12</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr"/>
       <c r="G97" s="5" t="n">
-        <v>345.2</v>
+        <v>1336.7</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>278</v>
+        <v/>
       </c>
       <c r="I97" s="5" t="n">
-        <v>39.1</v>
+        <v>171.3</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>41.5</v>
+        <v/>
       </c>
       <c r="K97" s="5" t="n">
-        <v>108.4</v>
+        <v>672.6</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.55</v>
+        <v>0.867</v>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
-          <t>Michael Evans, Ravi Tanaka, Jessica Patel, Thomas Mueller, Jennifer Xu</t>
+          <t>Yuki Williams, Emma Yamamoto, Yuki O'Brien</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Zenith Foods</t>
+          <t>Fathom Ltd</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -5206,59 +5190,158 @@
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>2018-02-07</t>
+          <t>2019-02-04</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
+          <t>2022-02-20</t>
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>749</v>
+        <v>664.4</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>1838.7</v>
+        <v>775</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>137.4</v>
+        <v>105.3</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>144</v>
+        <v>215.5</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>449.2</v>
+        <v>444.8</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0.791</v>
+        <v>0.32</v>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
-          <t>Yuki Davis, Amanda Kim</t>
+          <t>Olivia Ivanov, Rachel Lopez, Yuki Lopez, Ahmed Lopez, Olivia Nakamura</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Beacon Labs</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>1778</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>5041.3</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>490.8</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>558.4</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>938.6</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
+          <t>Hannah O'Brien, Olivia Vega</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
-        <is>
-          <t>Fund VI</t>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Junction Energy</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr"/>
+      <c r="G100" s="5" t="n">
+        <v>1308.1</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>243.5</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Ivanov, Jennifer Mueller, Sophie Fischer, Jennifer Evans</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Echo Foods</t>
+          <t>Iris Group</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -5268,52 +5351,52 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1708</v>
+        <v>641.5</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>4680.7</v>
+        <v>915.6</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>457.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>964.7</v>
+        <v>148.5</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>869.4</v>
+        <v>193.4</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>0.964</v>
+        <v>0.708</v>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Rossi, Laura O'Brien</t>
+          <t>Emma Lopez, Priya Zhang, Olivia Anderson, Jessica Ueno</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Fathom Energy</t>
+          <t>Fathom Tech</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -5323,103 +5406,107 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>2020-01-20</t>
+          <t>2018-04-10</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>1114.8</v>
+        <v>482.4</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>2664.4</v>
+        <v>920.7</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>136.6</v>
+        <v>107.4</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>293.2</v>
+        <v>111.1</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>174.8</v>
+        <v>392.9</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>0.411</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
-          <t>Yuki Schmidt, Rachel Gupta, Rachel Williams</t>
+          <t>Emma Schmidt, Laura Fischer, Laura Williams</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Cipher Media</t>
+          <t>Bloom Materials</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>2023-03-15</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr"/>
+          <t>2019-01-12</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>2022-11-26</t>
+        </is>
+      </c>
       <c r="G103" s="5" t="n">
-        <v>1261.8</v>
+        <v>900.4</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v/>
+        <v>1609.5</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>288.7</v>
+        <v>119.8</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v/>
+        <v>216.6</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>946.9</v>
+        <v>509.4</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0.699</v>
+        <v>0.73</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
-          <t>Rachel O'Brien, James Anderson, Amanda Lopez</t>
+          <t>Sophie Lopez, Daniel Rossi, James Evans, Jennifer Fischer</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Drift Foods</t>
+          <t>Ember Partners</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5429,52 +5516,52 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>2020-04-07</t>
+          <t>2020-02-28</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>905.6</v>
+        <v>1755.5</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>1948.4</v>
+        <v>3305.6</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>79.8</v>
+        <v>443.3</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>170.1</v>
+        <v>366.7</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>213.5</v>
+        <v>694.4</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>0.643</v>
+        <v>0.673</v>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
-          <t>Olivia Yamamoto, Priya Vega</t>
+          <t>Sarah Hassan, Michael Hassan, Priya Vega</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Glacier Systems</t>
+          <t>Xenith Foods</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -5484,52 +5571,52 @@
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
+          <t>2021-09-16</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1893.4</v>
+        <v>1070</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>6027.1</v>
+        <v>2120.6</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>389.4</v>
+        <v>171</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>710.3</v>
+        <v>407.1</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>975.8</v>
+        <v>761.5</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>0.16</v>
+        <v>0.885</v>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
-          <t>Matthew Lopez, Ahmed Mueller</t>
+          <t>Emma Anderson, Michael Vega</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Forge Logic</t>
+          <t>Lattice Inc</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -5539,158 +5626,55 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>2023-05-20</t>
+          <t>2018-12-24</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr"/>
       <c r="G106" s="5" t="n">
-        <v>177.8</v>
+        <v>1823.9</v>
       </c>
       <c r="H106" s="5" t="n">
         <v/>
       </c>
       <c r="I106" s="5" t="n">
-        <v>29</v>
+        <v>305</v>
       </c>
       <c r="J106" s="5" t="n">
         <v/>
       </c>
       <c r="K106" s="5" t="n">
-        <v>122.4</v>
+        <v>676</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.73</v>
+        <v>0.444</v>
       </c>
       <c r="M106" s="5" t="inlineStr">
         <is>
-          <t>Robert Patel, Elena Ivanov, Priya Tanaka, Ahmed Johnson, Matthew Mueller</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>Bloom Holdings</t>
-        </is>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>2023-10-27</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>2025-10-20</t>
-        </is>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>990.5</v>
-      </c>
-      <c r="H107" s="5" t="n">
-        <v>2139.8</v>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>273.9</v>
-      </c>
-      <c r="J107" s="5" t="n">
-        <v>364.3</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>491.2</v>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>Laura Johnson, Amanda Nakamura</t>
+          <t>Wei Davis, Wei Hassan, Robert Vega, Michael Evans, Matthew Lopez</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>Atlas Logistics</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>2022-05-11</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>2025-07-28</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>1118.1</v>
-      </c>
-      <c r="H108" s="5" t="n">
-        <v>3353.8</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>215.5</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>204.2</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>796.1</v>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="M108" s="5" t="inlineStr">
-        <is>
-          <t>Matthew Qureshi, Matthew Zhang, Jennifer Ueno, Jessica Schmidt, Mark Zhang</t>
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Fund VI</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>Xenith Networks</t>
+          <t>Junction Partners</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -5700,103 +5684,107 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1802.9</v>
+        <v>1421.3</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>4654.9</v>
+        <v>4623.9</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>228.9</v>
+        <v>152.1</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>251.3</v>
+        <v>259.5</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>291.4</v>
+        <v>256.7</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0.947</v>
+        <v>0.871</v>
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>Priya Kim, Jennifer Davis, Christopher Johnson, Amanda Nakamura</t>
+          <t>Matthew Brown, Matthew Johnson, Mark Mueller, Michael Chen, Ravi Nakamura</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Nimbus AG</t>
+          <t>Apex Dynamics</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="inlineStr"/>
+          <t>2020-05-23</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
       <c r="G110" s="5" t="n">
-        <v>1549.1</v>
+        <v>796.8</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v/>
+        <v>1983.7</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>311</v>
+        <v>122.4</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v/>
+        <v>198.7</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>1143</v>
+        <v>247</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0.202</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
-          <t>Priya O'Brien, Elena Yamamoto, Yuki Vega</t>
+          <t>Mark Nakamura, Wei Hassan, Emma Ivanov, Elena Williams, Emma Fischer</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>Nova Networks</t>
+          <t>Nova Partners</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -5806,48 +5794,48 @@
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-02-06</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr"/>
       <c r="G111" s="5" t="n">
-        <v>1943.8</v>
+        <v>539.7</v>
       </c>
       <c r="H111" s="5" t="n">
         <v/>
       </c>
       <c r="I111" s="5" t="n">
-        <v>202.1</v>
+        <v>75.8</v>
       </c>
       <c r="J111" s="5" t="n">
         <v/>
       </c>
       <c r="K111" s="5" t="n">
-        <v>292.9</v>
+        <v>42.5</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
-          <t>Sarah Ueno, Robert Kim, Andrew Brown, Sarah Evans</t>
+          <t>Jessica Brown, Laura Tanaka</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Meridian Energy</t>
+          <t>Yields Inc</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -5857,107 +5845,103 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
+          <t>2021-05-07</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>1354.9</v>
+        <v>1639.7</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>2554.5</v>
+        <v>4956.2</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>195.6</v>
+        <v>154.4</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>472.1</v>
+        <v>340.4</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>613.3</v>
+        <v>573.6</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0.424</v>
+        <v>0.841</v>
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
-          <t>Sarah Mueller, Hannah Tanaka, Priya Anderson, Andrew Chen, Jennifer Nakamura</t>
+          <t>Wei Mueller, James Davis, Priya Fischer</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>Cobalt Industries</t>
+          <t>Cobalt Solutions</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr"/>
       <c r="G113" s="5" t="n">
-        <v>1592.1</v>
+        <v>472.8</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>5322.8</v>
+        <v/>
       </c>
       <c r="I113" s="5" t="n">
-        <v>157.8</v>
+        <v>108.6</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>389.7</v>
+        <v/>
       </c>
       <c r="K113" s="5" t="n">
-        <v>494.1</v>
+        <v>367</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0.774</v>
+        <v>0.626</v>
       </c>
       <c r="M113" s="5" t="inlineStr">
         <is>
-          <t>Daniel Chen, Priya Mueller</t>
+          <t>Rachel Kim, Laura Brown</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Meridian SA</t>
+          <t>Lattice Health</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Toronto, CA</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -5967,48 +5951,48 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2023-06-21</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr"/>
       <c r="G114" s="5" t="n">
-        <v>1059.2</v>
+        <v>250.9</v>
       </c>
       <c r="H114" s="5" t="n">
         <v/>
       </c>
       <c r="I114" s="5" t="n">
-        <v>274.9</v>
+        <v>53.9</v>
       </c>
       <c r="J114" s="5" t="n">
         <v/>
       </c>
       <c r="K114" s="5" t="n">
-        <v>1070.1</v>
+        <v>144.9</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>0.741</v>
+        <v>0.532</v>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>Michael Lopez, Jennifer Xu, Elena Lopez</t>
+          <t>Christopher Anderson, Emma Vega</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>Vertex Solutions</t>
+          <t>Gravity Bio</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -6018,48 +6002,48 @@
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr"/>
       <c r="G115" s="5" t="n">
-        <v>1185.9</v>
+        <v>1545.9</v>
       </c>
       <c r="H115" s="5" t="n">
         <v/>
       </c>
       <c r="I115" s="5" t="n">
-        <v>316.3</v>
+        <v>288.7</v>
       </c>
       <c r="J115" s="5" t="n">
         <v/>
       </c>
       <c r="K115" s="5" t="n">
-        <v>826.1</v>
+        <v>1130.4</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>0.8</v>
+        <v>0.249</v>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>Hannah Anderson, James Vega, Christopher Kim, Yuki Anderson</t>
+          <t>Christopher Brown, Hannah Zhang, Hannah Vega</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Atlas Logic</t>
+          <t>Indigo AG</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -6069,103 +6053,107 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2021-04-05</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>298.6</v>
+        <v>371</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>501.7</v>
+        <v>956.2</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>50.4</v>
+        <v>72.2</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>111.1</v>
+        <v>104</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>43.9</v>
+        <v>118</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>0.805</v>
+        <v>0.309</v>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
-          <t>Laura Gupta, Olivia Chen, Olivia Mueller, David Xu</t>
+          <t>Wei Evans, Priya Kim</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Forge Systems</t>
+          <t>Polaris Media</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr"/>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
       <c r="G117" s="5" t="n">
-        <v>1385.4</v>
+        <v>1791</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v/>
+        <v>3954</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>382.4</v>
+        <v>377.2</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v/>
+        <v>739.3</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>926.4</v>
+        <v>361</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>0.914</v>
+        <v>0.615</v>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
-          <t>Sophie Zhang, Sophie Davis, Michael Brown, Sarah Tanaka</t>
+          <t>Thomas Davis, Sophie Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Tessera Industries</t>
+          <t>Echo AG</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -6175,103 +6163,99 @@
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2020-04-11</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr"/>
       <c r="G118" s="5" t="n">
-        <v>1708.3</v>
+        <v>907.9</v>
       </c>
       <c r="H118" s="5" t="n">
         <v/>
       </c>
       <c r="I118" s="5" t="n">
-        <v>179.7</v>
+        <v>151</v>
       </c>
       <c r="J118" s="5" t="n">
         <v/>
       </c>
       <c r="K118" s="5" t="n">
-        <v>666.7</v>
+        <v>252.7</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>0.801</v>
+        <v>0.659</v>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
-          <t>Thomas Yamamoto, James Johnson, Thomas Davis</t>
+          <t>Daniel Ueno, Wei Gupta</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Pharma</t>
+          <t>Iris Systems</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>2022-06-04</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
+          <t>2021-12-24</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr"/>
       <c r="G119" s="5" t="n">
-        <v>564.1</v>
+        <v>226.5</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>842.6</v>
+        <v/>
       </c>
       <c r="I119" s="5" t="n">
-        <v>78.59999999999999</v>
+        <v>49.5</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>91.40000000000001</v>
+        <v/>
       </c>
       <c r="K119" s="5" t="n">
-        <v>299.6</v>
+        <v>46.1</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>0.751</v>
+        <v>0.436</v>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
-          <t>Jessica Evans, Olivia Mueller</t>
+          <t>David Xu, Daniel O'Brien</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Gravity GmbH</t>
+          <t>Delta Materials</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -6281,52 +6265,52 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>2021-12-11</t>
+          <t>2023-04-26</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-06-28</t>
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>1734.3</v>
+        <v>761.7</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>5934.2</v>
+        <v>1108.7</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>196</v>
+        <v>65.7</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>157.9</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>618.9</v>
+        <v>281.2</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>0.236</v>
+        <v>0.264</v>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
-          <t>Thomas Patel, James Ueno, Daniel Rossi, Ahmed Nakamura</t>
+          <t>Sophie Kim, David Williams</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Health</t>
+          <t>Forge Labs</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -6336,209 +6320,205 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr"/>
       <c r="G121" s="5" t="n">
-        <v>620.3</v>
+        <v>914</v>
       </c>
       <c r="H121" s="5" t="n">
         <v/>
       </c>
       <c r="I121" s="5" t="n">
-        <v>96.90000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="J121" s="5" t="n">
         <v/>
       </c>
       <c r="K121" s="5" t="n">
-        <v>65.5</v>
+        <v>215.2</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.61</v>
+        <v>0.728</v>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>Mark Mueller, Michael Ivanov, Elena Zhang, Rachel Ivanov</t>
+          <t>Priya Mueller, James Patel, Elena Chen</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Ember Corp</t>
+          <t>Helix Inc</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>2021-04-18</t>
-        </is>
-      </c>
-      <c r="F122" s="5" t="inlineStr"/>
+          <t>2020-02-11</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
       <c r="G122" s="5" t="n">
-        <v>1540.4</v>
+        <v>838.1</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v/>
+        <v>2720.6</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>275</v>
+        <v>185.9</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v/>
+        <v>214</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>943.1</v>
+        <v>688</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0.205</v>
+        <v>0.192</v>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
-          <t>Ravi Patel, Matthew Vega</t>
+          <t>Ravi O'Brien, Jessica Kim</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>Fathom Pharma</t>
+          <t>Krypton Media</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>2021-02-06</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
-      </c>
+          <t>2022-12-04</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr"/>
       <c r="G123" s="5" t="n">
-        <v>1634.1</v>
+        <v>1585.4</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>4326.8</v>
+        <v/>
       </c>
       <c r="I123" s="5" t="n">
-        <v>320.4</v>
+        <v>430.8</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>441.3</v>
+        <v/>
       </c>
       <c r="K123" s="5" t="n">
-        <v>1195</v>
+        <v>256.2</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>0.182</v>
+        <v>0.729</v>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
-          <t>Elena Xu, James Tanaka, Ravi Xu, Wei Johnson, Elena Tanaka</t>
+          <t>Wei Xu, Elena Yamamoto, Mark Patel, Mark Xu</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Krypton SA</t>
+          <t>Junction Health</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>Sydney, AU</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>2023-08-18</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
+          <t>2022-10-15</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr"/>
       <c r="G124" s="5" t="n">
-        <v>780.6</v>
+        <v>1937.7</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>1886.1</v>
+        <v/>
       </c>
       <c r="I124" s="5" t="n">
-        <v>185.1</v>
+        <v>455.6</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>327.9</v>
+        <v/>
       </c>
       <c r="K124" s="5" t="n">
-        <v>747.8</v>
+        <v>1427</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>0.804</v>
+        <v>0.417</v>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
-          <t>Robert Evans, Wei Hassan, Sarah Anderson</t>
+          <t>Emma Anderson, Rachel Fischer, Elena Williams</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>Nova Logic</t>
+          <t>Orion Dynamics</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -6548,52 +6528,52 @@
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2021-06-24</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>419.6</v>
+        <v>90.3</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>1117.4</v>
+        <v>112</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>56.7</v>
+        <v>22.6</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>131.8</v>
+        <v>29.3</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>93.40000000000001</v>
+        <v>25</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.336</v>
+        <v>0.15</v>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
-          <t>Andrew Hassan, David Lopez</t>
+          <t>Robert Tanaka, Ravi Xu, Andrew Brown, Jennifer Lopez, David Schmidt</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Gravity Materials</t>
+          <t>Yields Industries</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -6603,48 +6583,48 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>2021-12-20</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr"/>
       <c r="G126" s="5" t="n">
-        <v>803.6</v>
+        <v>553.4</v>
       </c>
       <c r="H126" s="5" t="n">
         <v/>
       </c>
       <c r="I126" s="5" t="n">
-        <v>224.5</v>
+        <v>119.2</v>
       </c>
       <c r="J126" s="5" t="n">
         <v/>
       </c>
       <c r="K126" s="5" t="n">
-        <v>338</v>
+        <v>396.6</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>0.877</v>
+        <v>0.502</v>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
-          <t>Sophie Gupta, Elena Williams, Mark Nakamura, Robert Mueller, Jessica Brown</t>
+          <t>Rachel Kim, Matthew Mueller, James Lopez, Hannah Zhang, Olivia Yamamoto</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>Wavelength GmbH</t>
+          <t>Ember Logic</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>London, UK</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -6654,52 +6634,52 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2021-01-13</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1224.6</v>
+        <v>231.2</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>2362.3</v>
+        <v>714.5</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>188.9</v>
+        <v>41</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>404.1</v>
+        <v>57.7</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>272.2</v>
+        <v>40.6</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>0.719</v>
+        <v>0.405</v>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Fischer, Daniel Williams</t>
+          <t>Thomas Zhang, Priya Chen, David Davis</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Lattice Industries</t>
+          <t>Delta Dynamics</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -6709,86 +6689,82 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>2022-12-02</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr"/>
       <c r="G128" s="5" t="n">
-        <v>1085.5</v>
+        <v>1928.3</v>
       </c>
       <c r="H128" s="5" t="n">
         <v/>
       </c>
       <c r="I128" s="5" t="n">
-        <v>268.5</v>
+        <v>420.1</v>
       </c>
       <c r="J128" s="5" t="n">
         <v/>
       </c>
       <c r="K128" s="5" t="n">
-        <v>1170.5</v>
+        <v>1879.7</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>0.537</v>
+        <v>0.729</v>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
-          <t>Jessica Tanaka, Jessica Tanaka, Wei Vega, Jessica Mueller, Hannah Fischer</t>
+          <t>Ahmed Rossi, Emma Kim, Yuki Lopez</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>Forge Partners</t>
+          <t>Fathom Pharma</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Zurich, CH</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>2023-02-06</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr"/>
       <c r="G129" s="5" t="n">
-        <v>1156.1</v>
+        <v>1543.2</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>2170.3</v>
+        <v/>
       </c>
       <c r="I129" s="5" t="n">
-        <v>170.5</v>
+        <v>179.9</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>224.9</v>
+        <v/>
       </c>
       <c r="K129" s="5" t="n">
-        <v>456.8</v>
+        <v>276.7</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.163</v>
+        <v>0.228</v>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
-          <t>James Kim, Matthew Chen, Ravi Kim</t>
+          <t>Amanda Kim, Matthew Fischer, Rachel Ueno, Hannah Hassan, Andrew O'Brien</t>
         </is>
       </c>
     </row>
